--- a/healthcare_forms/013_gym_health_questionnaire_form--healthcare_forms.xlsx
+++ b/healthcare_forms/013_gym_health_questionnaire_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
